--- a/results/pooled_results_OR_multi_exposure_models_cold_parent_excludes_rheumatism.xlsx
+++ b/results/pooled_results_OR_multi_exposure_models_cold_parent_excludes_rheumatism.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD026A68-C804-482D-8BBE-5514B5948A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1579705-574F-4CD9-B3F5-EF086D641689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{797B858C-DA94-466A-A931-46BE830858D9}"/>
   </bookViews>
@@ -340,6 +340,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -350,9 +353,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -739,30 +739,30 @@
       <c r="C5" s="5"/>
     </row>
     <row r="6" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
-      <c r="I6" s="18" t="s">
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="I6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="20"/>
-      <c r="N6" s="18" t="s">
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="21"/>
+      <c r="N6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="20"/>
-      <c r="S6" s="18" t="s">
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="21"/>
+      <c r="S6" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="21"/>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
       <c r="D7" s="9"/>
@@ -837,34 +837,34 @@
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="21"/>
+      <c r="E9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="22"/>
       <c r="G9" s="13"/>
       <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="J9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="21"/>
+      <c r="J9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="22"/>
       <c r="L9" s="13"/>
       <c r="N9" s="1">
         <v>1</v>
       </c>
-      <c r="O9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="P9" s="21"/>
+      <c r="O9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="22"/>
       <c r="Q9" s="13"/>
       <c r="S9" s="1">
         <v>1</v>
       </c>
-      <c r="T9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="U9" s="21"/>
+      <c r="T9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="U9" s="22"/>
       <c r="V9" s="13"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -998,10 +998,10 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="22"/>
+      <c r="E13" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="18"/>
       <c r="G13" s="13"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1090,10 +1090,10 @@
       <c r="I18" s="1">
         <v>1</v>
       </c>
-      <c r="J18" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="22"/>
+      <c r="J18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="18"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1178,10 +1178,10 @@
       <c r="N22" s="1">
         <v>1</v>
       </c>
-      <c r="O22" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P22" s="22"/>
+      <c r="O22" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="18"/>
       <c r="Q22" s="13"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -1215,16 +1215,16 @@
         <v>2</v>
       </c>
       <c r="G24" s="13"/>
-      <c r="N24" s="1">
+      <c r="N24" s="12">
         <v>2.5775706999999999</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="12">
         <v>1.1668987</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="12">
         <v>5.6936140000000002</v>
       </c>
-      <c r="Q24" s="13">
+      <c r="Q24" s="14">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="S24" s="1"/>
@@ -1281,10 +1281,10 @@
       <c r="S27" s="1">
         <v>1</v>
       </c>
-      <c r="T27" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="U27" s="22"/>
+      <c r="T27" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U27" s="18"/>
       <c r="V27" s="13"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
@@ -1511,34 +1511,34 @@
       <c r="D36" s="1">
         <v>1</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="22"/>
+      <c r="E36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="18"/>
       <c r="G36" s="13"/>
       <c r="I36" s="1">
         <v>1</v>
       </c>
-      <c r="J36" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="K36" s="22"/>
+      <c r="J36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K36" s="18"/>
       <c r="L36" s="13"/>
       <c r="N36" s="1">
         <v>1</v>
       </c>
-      <c r="O36" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P36" s="22"/>
+      <c r="O36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="18"/>
       <c r="Q36" s="13"/>
       <c r="S36" s="1">
         <v>1</v>
       </c>
-      <c r="T36" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="U36" s="22"/>
+      <c r="T36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U36" s="18"/>
       <c r="V36" s="13"/>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.3">
@@ -1672,34 +1672,34 @@
       <c r="D40" s="1">
         <v>1</v>
       </c>
-      <c r="E40" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="22"/>
+      <c r="E40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="18"/>
       <c r="G40" s="13"/>
       <c r="I40" s="1">
         <v>1</v>
       </c>
-      <c r="J40" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="K40" s="22"/>
+      <c r="J40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40" s="18"/>
       <c r="L40" s="13"/>
       <c r="N40" s="1">
         <v>1</v>
       </c>
-      <c r="O40" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P40" s="22"/>
+      <c r="O40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P40" s="18"/>
       <c r="Q40" s="13"/>
       <c r="S40" s="1">
         <v>1</v>
       </c>
-      <c r="T40" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="U40" s="22"/>
+      <c r="T40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U40" s="18"/>
       <c r="V40" s="13"/>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.3">
@@ -1780,34 +1780,34 @@
       <c r="D43" s="1">
         <v>1</v>
       </c>
-      <c r="E43" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F43" s="22"/>
+      <c r="E43" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="18"/>
       <c r="G43" s="13"/>
       <c r="I43" s="1">
         <v>1</v>
       </c>
-      <c r="J43" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="K43" s="22"/>
+      <c r="J43" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K43" s="18"/>
       <c r="L43" s="13"/>
       <c r="N43" s="1">
         <v>1</v>
       </c>
-      <c r="O43" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P43" s="22"/>
+      <c r="O43" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P43" s="18"/>
       <c r="Q43" s="13"/>
       <c r="S43" s="1">
         <v>1</v>
       </c>
-      <c r="T43" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="U43" s="22"/>
+      <c r="T43" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U43" s="18"/>
       <c r="V43" s="13"/>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.3">
@@ -1941,34 +1941,34 @@
       <c r="D47" s="1">
         <v>1</v>
       </c>
-      <c r="E47" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F47" s="22"/>
+      <c r="E47" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="18"/>
       <c r="G47" s="13"/>
       <c r="I47" s="1">
         <v>1</v>
       </c>
-      <c r="J47" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="K47" s="22"/>
+      <c r="J47" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K47" s="18"/>
       <c r="L47" s="13"/>
       <c r="N47" s="1">
         <v>1</v>
       </c>
-      <c r="O47" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P47" s="22"/>
+      <c r="O47" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P47" s="18"/>
       <c r="Q47" s="13"/>
       <c r="S47" s="1">
         <v>1</v>
       </c>
-      <c r="T47" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="U47" s="22"/>
+      <c r="T47" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U47" s="18"/>
       <c r="V47" s="13"/>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.3">
@@ -2049,34 +2049,34 @@
       <c r="D50" s="1">
         <v>1</v>
       </c>
-      <c r="E50" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="22"/>
+      <c r="E50" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="18"/>
       <c r="G50" s="13"/>
       <c r="I50" s="1">
         <v>1</v>
       </c>
-      <c r="J50" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="K50" s="22"/>
+      <c r="J50" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50" s="18"/>
       <c r="L50" s="13"/>
       <c r="N50" s="1">
         <v>1</v>
       </c>
-      <c r="O50" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P50" s="22"/>
+      <c r="O50" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P50" s="18"/>
       <c r="Q50" s="13"/>
       <c r="S50" s="1">
         <v>1</v>
       </c>
-      <c r="T50" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="U50" s="22"/>
+      <c r="T50" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U50" s="18"/>
       <c r="V50" s="13"/>
     </row>
     <row r="51" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2139,6 +2139,30 @@
     <row r="52" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="T40:U40"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="T43:U43"/>
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="J47:K47"/>
     <mergeCell ref="O47:P47"/>
@@ -2147,30 +2171,6 @@
     <mergeCell ref="J50:K50"/>
     <mergeCell ref="O50:P50"/>
     <mergeCell ref="T50:U50"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="T40:U40"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="S6:V6"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="T9:U9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
